--- a/resultados/Relatorio_Comportamento_Por_Setor_suplementar.xlsx
+++ b/resultados/Relatorio_Comportamento_Por_Setor_suplementar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e124796\Gama_Workspace\ABMS-WP\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7BD0DD-7B99-4F9F-BAC9-464F8E4D12A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFC7452-E729-4E04-80E7-42DA3723270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{445F844C-0130-4D0C-B964-73D8B6288AE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{445F844C-0130-4D0C-B964-73D8B6288AE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Relatorio_Comportamento_Por_Set" sheetId="1" r:id="rId1"/>
@@ -1472,9 +1472,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1520,7 +1526,31 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="9">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1553,18 +1583,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{03D633FF-F1D4-408F-9EFA-36DAD7777B72}" name="Tabela1" displayName="Tabela1" ref="A3:I67" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{03D633FF-F1D4-408F-9EFA-36DAD7777B72}" name="Tabela1" displayName="Tabela1" ref="A3:I67" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A3:I67" xr:uid="{03D633FF-F1D4-408F-9EFA-36DAD7777B72}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F114BD9D-F836-4E81-9C0D-42C712A2BA17}" name="CD_SETOR"/>
-    <tableColumn id="2" xr3:uid="{267404A4-B920-4FF5-BAE6-0BABA419D552}" name="total_consumers"/>
-    <tableColumn id="3" xr3:uid="{716BA909-2813-4B4B-956B-9C637273366A}" name="environmentalist_count"/>
-    <tableColumn id="4" xr3:uid="{B636D881-C0A2-4B2D-8D75-DEB5CB3010DA}" name="moderate_count"/>
-    <tableColumn id="5" xr3:uid="{4D2C7404-2A69-41A5-A6FF-C004D049244A}" name="wasteful_count"/>
-    <tableColumn id="6" xr3:uid="{6326E927-75E0-423B-8CEE-FD7705FC2299}" name="avg_daily_consumption"/>
-    <tableColumn id="7" xr3:uid="{90F277D3-9834-4B89-AC3C-DCEBB634BE7C}" name="pct_environmentalist"/>
-    <tableColumn id="8" xr3:uid="{D2778D66-1D7D-4BC3-92DD-0AE58A308CF0}" name="pct_moderate"/>
-    <tableColumn id="9" xr3:uid="{86358FF2-A19D-4283-86F7-ECE58932237E}" name="pct_wasteful"/>
+    <tableColumn id="2" xr3:uid="{267404A4-B920-4FF5-BAE6-0BABA419D552}" name="total_consumers" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{716BA909-2813-4B4B-956B-9C637273366A}" name="environmentalist_count" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{B636D881-C0A2-4B2D-8D75-DEB5CB3010DA}" name="moderate_count" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{4D2C7404-2A69-41A5-A6FF-C004D049244A}" name="wasteful_count" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{6326E927-75E0-423B-8CEE-FD7705FC2299}" name="avg_daily_consumption" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{90F277D3-9834-4B89-AC3C-DCEBB634BE7C}" name="pct_environmentalist" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{D2778D66-1D7D-4BC3-92DD-0AE58A308CF0}" name="pct_moderate" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{86358FF2-A19D-4283-86F7-ECE58932237E}" name="pct_wasteful" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1895,39 +1925,39 @@
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1"/>
+      <c r="I1" s="3"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1937,25 +1967,25 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J3" s="1"/>
@@ -1964,28 +1994,28 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>658</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>314</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>76</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>268</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1993,28 +2023,28 @@
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>582</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>319</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>49</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>214</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2022,28 +2052,28 @@
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>554</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>316</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>38</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>200</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2051,28 +2081,28 @@
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>489</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>296</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>54</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>139</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2080,28 +2110,28 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>453</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>292</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>33</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>128</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2109,28 +2139,28 @@
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>445</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>248</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>30</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>167</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2138,28 +2168,28 @@
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>413</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>206</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>30</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>177</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2167,28 +2197,28 @@
       <c r="A11" t="s">
         <v>45</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>403</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>220</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>43</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>140</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2196,28 +2226,28 @@
       <c r="A12" t="s">
         <v>50</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>394</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>223</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>35</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>136</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="2" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2225,28 +2255,28 @@
       <c r="A13" t="s">
         <v>55</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>354</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>220</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>40</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>94</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="2" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2254,28 +2284,28 @@
       <c r="A14" t="s">
         <v>60</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>351</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>152</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>37</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>162</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2283,28 +2313,28 @@
       <c r="A15" t="s">
         <v>65</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>348</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>206</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>49</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>93</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="2" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2312,28 +2342,28 @@
       <c r="A16" t="s">
         <v>70</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>343</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>211</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>28</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>104</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2341,28 +2371,28 @@
       <c r="A17" t="s">
         <v>75</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>334</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>224</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>34</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>76</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="2" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2370,28 +2400,28 @@
       <c r="A18" t="s">
         <v>80</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>323</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>232</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>25</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>66</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="2" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2399,28 +2429,28 @@
       <c r="A19" t="s">
         <v>85</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>302</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>72</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>23</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>207</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="2" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2428,28 +2458,28 @@
       <c r="A20" t="s">
         <v>90</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>300</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>195</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>25</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>80</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="2" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2457,28 +2487,28 @@
       <c r="A21" t="s">
         <v>95</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>295</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>158</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>37</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>100</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="2" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2486,28 +2516,28 @@
       <c r="A22" t="s">
         <v>100</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>274</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>153</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>22</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>99</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="2" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2515,28 +2545,28 @@
       <c r="A23" t="s">
         <v>105</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>273</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>151</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>26</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>96</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="2" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2544,28 +2574,28 @@
       <c r="A24" t="s">
         <v>110</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>272</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>78</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>18</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>176</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2573,28 +2603,28 @@
       <c r="A25" t="s">
         <v>115</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>268</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>125</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>27</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>116</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2602,28 +2632,28 @@
       <c r="A26" t="s">
         <v>120</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>267</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>195</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>22</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>50</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="2" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2631,28 +2661,28 @@
       <c r="A27" t="s">
         <v>125</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>254</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>152</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>21</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>81</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="2" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2660,28 +2690,28 @@
       <c r="A28" t="s">
         <v>130</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>238</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>154</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>21</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>63</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="2" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2689,28 +2719,28 @@
       <c r="A29" t="s">
         <v>134</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>234</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>143</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>17</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>74</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="2" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2718,28 +2748,28 @@
       <c r="A30" t="s">
         <v>138</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>228</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>178</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>9</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <v>41</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="2" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2747,28 +2777,28 @@
       <c r="A31" t="s">
         <v>143</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>222</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>152</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>19</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <v>51</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="2" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2776,28 +2806,28 @@
       <c r="A32" t="s">
         <v>148</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>215</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>97</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>22</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <v>96</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="2" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2805,28 +2835,28 @@
       <c r="A33" t="s">
         <v>153</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <v>210</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>125</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>7</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="2">
         <v>78</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="2" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2834,28 +2864,28 @@
       <c r="A34" t="s">
         <v>158</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <v>209</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>120</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>19</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>70</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="2" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2863,28 +2893,28 @@
       <c r="A35" t="s">
         <v>163</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="2">
         <v>190</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>140</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>7</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <v>43</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="2" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2892,28 +2922,28 @@
       <c r="A36" t="s">
         <v>168</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <v>188</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>65</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>17</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <v>106</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="2" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2921,28 +2951,28 @@
       <c r="A37" t="s">
         <v>173</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>186</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>108</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>13</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <v>65</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2950,28 +2980,28 @@
       <c r="A38" t="s">
         <v>178</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
         <v>183</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>80</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>17</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="2">
         <v>86</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="2" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2979,28 +3009,28 @@
       <c r="A39" t="s">
         <v>183</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
         <v>173</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>64</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>20</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <v>89</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="2" t="s">
         <v>187</v>
       </c>
     </row>
@@ -3008,28 +3038,28 @@
       <c r="A40" t="s">
         <v>188</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
         <v>173</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>108</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>15</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>50</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="2" t="s">
         <v>192</v>
       </c>
     </row>
@@ -3037,28 +3067,28 @@
       <c r="A41" t="s">
         <v>193</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
         <v>173</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <v>125</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>14</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <v>34</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="2" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3066,28 +3096,28 @@
       <c r="A42" t="s">
         <v>198</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
         <v>172</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <v>73</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>19</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <v>80</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="2" t="s">
         <v>202</v>
       </c>
     </row>
@@ -3095,28 +3125,28 @@
       <c r="A43" t="s">
         <v>203</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
         <v>163</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <v>116</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>13</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="2">
         <v>34</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="2" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3124,28 +3154,28 @@
       <c r="A44" t="s">
         <v>208</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="2">
         <v>162</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <v>104</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <v>12</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="2">
         <v>46</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="2" t="s">
         <v>212</v>
       </c>
     </row>
@@ -3153,28 +3183,28 @@
       <c r="A45" t="s">
         <v>213</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="2">
         <v>160</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
         <v>76</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <v>16</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="2">
         <v>68</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="2" t="s">
         <v>217</v>
       </c>
     </row>
@@ -3182,28 +3212,28 @@
       <c r="A46" t="s">
         <v>218</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="2">
         <v>158</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2">
         <v>104</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <v>15</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="2">
         <v>39</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="2" t="s">
         <v>222</v>
       </c>
     </row>
@@ -3211,28 +3241,28 @@
       <c r="A47" t="s">
         <v>223</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="2">
         <v>157</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2">
         <v>112</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>12</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="2">
         <v>33</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="2" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3240,28 +3270,28 @@
       <c r="A48" t="s">
         <v>228</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="2">
         <v>153</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2">
         <v>99</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>15</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <v>39</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="2" t="s">
         <v>231</v>
       </c>
     </row>
@@ -3269,28 +3299,28 @@
       <c r="A49" t="s">
         <v>232</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="2">
         <v>151</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2">
         <v>111</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <v>10</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="2">
         <v>30</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="2" t="s">
         <v>235</v>
       </c>
     </row>
@@ -3298,28 +3328,28 @@
       <c r="A50" t="s">
         <v>236</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="2">
         <v>146</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2">
         <v>67</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="2">
         <v>21</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="2">
         <v>58</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="2" t="s">
         <v>240</v>
       </c>
     </row>
@@ -3327,28 +3357,28 @@
       <c r="A51" t="s">
         <v>241</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="2">
         <v>138</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="2">
         <v>43</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <v>14</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="2">
         <v>81</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="2" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3356,28 +3386,28 @@
       <c r="A52" t="s">
         <v>246</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="2">
         <v>138</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="2">
         <v>92</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <v>16</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="2">
         <v>30</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="2" t="s">
         <v>250</v>
       </c>
     </row>
@@ -3385,28 +3415,28 @@
       <c r="A53" t="s">
         <v>251</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="2">
         <v>136</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2">
         <v>59</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>15</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="2">
         <v>62</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="2" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3414,28 +3444,28 @@
       <c r="A54" t="s">
         <v>256</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="2">
         <v>127</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="2">
         <v>43</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <v>8</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="2">
         <v>76</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="2" t="s">
         <v>127</v>
       </c>
     </row>
@@ -3443,28 +3473,28 @@
       <c r="A55" t="s">
         <v>260</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="2">
         <v>118</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="2">
         <v>46</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <v>14</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="2">
         <v>58</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G55" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="2" t="s">
         <v>264</v>
       </c>
     </row>
@@ -3472,28 +3502,28 @@
       <c r="A56" t="s">
         <v>265</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="2">
         <v>105</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="2">
         <v>59</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <v>8</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="2">
         <v>38</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G56" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="2" t="s">
         <v>268</v>
       </c>
     </row>
@@ -3501,28 +3531,28 @@
       <c r="A57" t="s">
         <v>269</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="2">
         <v>103</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="2">
         <v>27</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <v>6</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="2">
         <v>70</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="2" t="s">
         <v>273</v>
       </c>
     </row>
@@ -3530,28 +3560,28 @@
       <c r="A58" t="s">
         <v>274</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="2">
         <v>97</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="2">
         <v>21</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>8</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="2">
         <v>68</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="2" t="s">
         <v>278</v>
       </c>
     </row>
@@ -3559,28 +3589,28 @@
       <c r="A59" t="s">
         <v>279</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="2">
         <v>91</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="2">
         <v>21</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <v>2</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="2">
         <v>68</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="2" t="s">
         <v>283</v>
       </c>
     </row>
@@ -3588,28 +3618,28 @@
       <c r="A60" t="s">
         <v>284</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="2">
         <v>87</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="2">
         <v>60</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <v>13</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="2">
         <v>14</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="2" t="s">
         <v>288</v>
       </c>
     </row>
@@ -3617,28 +3647,28 @@
       <c r="A61" t="s">
         <v>289</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="2">
         <v>83</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="2">
         <v>32</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>10</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="2">
         <v>41</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="2" t="s">
         <v>293</v>
       </c>
     </row>
@@ -3646,28 +3676,28 @@
       <c r="A62" t="s">
         <v>294</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="2">
         <v>83</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="2">
         <v>39</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <v>8</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="2">
         <v>36</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="2" t="s">
         <v>297</v>
       </c>
     </row>
@@ -3675,28 +3705,28 @@
       <c r="A63" t="s">
         <v>298</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="2">
         <v>79</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="2">
         <v>35</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <v>6</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="2">
         <v>38</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="2" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3704,28 +3734,28 @@
       <c r="A64" t="s">
         <v>303</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="2">
         <v>77</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="2">
         <v>51</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="2">
         <v>6</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="2">
         <v>20</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="2" t="s">
         <v>307</v>
       </c>
     </row>
@@ -3733,28 +3763,28 @@
       <c r="A65" t="s">
         <v>308</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="2">
         <v>66</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="2">
         <v>24</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="2">
         <v>5</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="2">
         <v>37</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="2" t="s">
         <v>312</v>
       </c>
     </row>
@@ -3762,28 +3792,28 @@
       <c r="A66" t="s">
         <v>313</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="2">
         <v>23</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="2">
         <v>11</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="2">
         <v>2</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="2">
         <v>10</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="2" t="s">
         <v>317</v>
       </c>
     </row>
@@ -3791,28 +3821,28 @@
       <c r="A67" t="s">
         <v>318</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="2">
         <v>1</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="2">
         <v>0</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="2">
         <v>0</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="2">
         <v>1</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="2" t="s">
         <v>321</v>
       </c>
     </row>
